--- a/antibiotic_list2.xlsx
+++ b/antibiotic_list2.xlsx
@@ -10,6 +10,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$E$246</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -20,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="302">
   <si>
     <t xml:space="preserve">Antibiotic</t>
   </si>
@@ -205,9 +208,6 @@
     <t xml:space="preserve">Other-cephalosporins</t>
   </si>
   <si>
-    <t xml:space="preserve">cephalosporins</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cefixime</t>
   </si>
   <si>
@@ -322,9 +322,6 @@
     <t xml:space="preserve">Monobactams</t>
   </si>
   <si>
-    <t xml:space="preserve">beta lactam and related</t>
-  </si>
-  <si>
     <t xml:space="preserve">Carumonam</t>
   </si>
   <si>
@@ -379,9 +376,6 @@
     <t xml:space="preserve">Aspoxicillin</t>
   </si>
   <si>
-    <t xml:space="preserve">Penicillins </t>
-  </si>
-  <si>
     <t xml:space="preserve">Azidocillin</t>
   </si>
   <si>
@@ -607,7 +601,7 @@
     <t xml:space="preserve">Amphenicols</t>
   </si>
   <si>
-    <t xml:space="preserve">other</t>
+    <t xml:space="preserve">Other</t>
   </si>
   <si>
     <t xml:space="preserve">Clofoctol</t>
@@ -889,7 +883,7 @@
     <t xml:space="preserve">Glycylcyclines</t>
   </si>
   <si>
-    <t xml:space="preserve">tetracyclines and related</t>
+    <t xml:space="preserve">Tetracyclines and related</t>
   </si>
   <si>
     <t xml:space="preserve">Chlortetracycline</t>
@@ -944,7 +938,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1001,6 +995,17 @@
       <name val="Arial Nova Light"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1064,7 +1069,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1093,6 +1098,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1102,6 +1115,39 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00B0F0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF46B1E1"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1163,6 +1209,10 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1339,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+  <sheetPr filterMode="true">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E246"/>
@@ -1370,7 +1420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1387,7 +1437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
@@ -1404,7 +1454,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -1421,7 +1471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
@@ -1438,7 +1488,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -1455,7 +1505,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
@@ -1472,7 +1522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
@@ -1489,7 +1539,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -1506,7 +1556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -1523,7 +1573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>17</v>
       </c>
@@ -1540,7 +1590,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
@@ -1557,7 +1607,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>19</v>
       </c>
@@ -1574,7 +1624,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -1591,7 +1641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>21</v>
       </c>
@@ -1608,7 +1658,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
@@ -1625,7 +1675,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>24</v>
       </c>
@@ -1642,7 +1692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>25</v>
       </c>
@@ -2058,7 +2108,7 @@
         <v>60</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>29</v>
@@ -2069,7 +2119,7 @@
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>53</v>
@@ -2086,7 +2136,7 @@
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>53</v>
@@ -2103,7 +2153,7 @@
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>41</v>
@@ -2120,7 +2170,7 @@
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>41</v>
@@ -2137,7 +2187,7 @@
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>53</v>
@@ -2154,7 +2204,7 @@
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>41</v>
@@ -2171,7 +2221,7 @@
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>53</v>
@@ -2188,7 +2238,7 @@
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>41</v>
@@ -2205,7 +2255,7 @@
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>57</v>
@@ -2222,7 +2272,7 @@
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>53</v>
@@ -2239,7 +2289,7 @@
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>41</v>
@@ -2256,7 +2306,7 @@
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>41</v>
@@ -2273,7 +2323,7 @@
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>41</v>
@@ -2290,7 +2340,7 @@
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>57</v>
@@ -2307,7 +2357,7 @@
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>53</v>
@@ -2324,7 +2374,7 @@
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>57</v>
@@ -2341,7 +2391,7 @@
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>53</v>
@@ -2358,7 +2408,7 @@
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>41</v>
@@ -2375,7 +2425,7 @@
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>38</v>
@@ -2392,7 +2442,7 @@
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>38</v>
@@ -2409,7 +2459,7 @@
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>53</v>
@@ -2426,10 +2476,10 @@
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>39</v>
@@ -2443,7 +2493,7 @@
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>53</v>
@@ -2460,7 +2510,7 @@
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>53</v>
@@ -2477,7 +2527,7 @@
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>53</v>
@@ -2494,7 +2544,7 @@
     </row>
     <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>38</v>
@@ -2511,7 +2561,7 @@
     </row>
     <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>53</v>
@@ -2528,7 +2578,7 @@
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>53</v>
@@ -2545,10 +2595,10 @@
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>39</v>
@@ -2562,10 +2612,10 @@
     </row>
     <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>39</v>
@@ -2579,7 +2629,7 @@
     </row>
     <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>53</v>
@@ -2596,7 +2646,7 @@
     </row>
     <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>41</v>
@@ -2613,7 +2663,7 @@
     </row>
     <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>41</v>
@@ -2630,7 +2680,7 @@
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>53</v>
@@ -2647,7 +2697,7 @@
     </row>
     <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>41</v>
@@ -2664,16 +2714,16 @@
     </row>
     <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B78" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="C78" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>8</v>
@@ -2681,16 +2731,16 @@
     </row>
     <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>8</v>
@@ -2698,16 +2748,16 @@
     </row>
     <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B80" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="D80" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>8</v>
@@ -2715,16 +2765,16 @@
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>8</v>
@@ -2732,16 +2782,16 @@
     </row>
     <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>8</v>
@@ -2749,16 +2799,16 @@
     </row>
     <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>8</v>
@@ -2766,16 +2816,16 @@
     </row>
     <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>8</v>
@@ -2783,16 +2833,16 @@
     </row>
     <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>8</v>
@@ -2800,16 +2850,16 @@
     </row>
     <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>8</v>
@@ -2817,16 +2867,16 @@
     </row>
     <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>8</v>
@@ -2834,16 +2884,16 @@
     </row>
     <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>8</v>
@@ -2851,16 +2901,16 @@
     </row>
     <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>8</v>
@@ -2868,16 +2918,16 @@
     </row>
     <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>8</v>
@@ -2885,16 +2935,16 @@
     </row>
     <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>8</v>
@@ -2902,16 +2952,16 @@
     </row>
     <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>8</v>
@@ -2919,16 +2969,16 @@
     </row>
     <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>8</v>
@@ -2936,16 +2986,16 @@
     </row>
     <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>8</v>
@@ -2953,16 +3003,16 @@
     </row>
     <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B95" s="6" t="s">
         <v>119</v>
       </c>
+      <c r="B95" s="7" t="s">
+        <v>114</v>
+      </c>
       <c r="C95" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>8</v>
@@ -2970,16 +3020,16 @@
     </row>
     <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>8</v>
@@ -2987,16 +3037,16 @@
     </row>
     <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>8</v>
@@ -3004,16 +3054,16 @@
     </row>
     <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>8</v>
@@ -3021,16 +3071,16 @@
     </row>
     <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>8</v>
@@ -3038,16 +3088,16 @@
     </row>
     <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>119</v>
+        <v>124</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>8</v>
@@ -3055,16 +3105,16 @@
     </row>
     <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>8</v>
@@ -3072,16 +3122,16 @@
     </row>
     <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>119</v>
+        <v>126</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>8</v>
@@ -3089,16 +3139,16 @@
     </row>
     <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>119</v>
+        <v>127</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>8</v>
@@ -3106,16 +3156,16 @@
     </row>
     <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>119</v>
+        <v>128</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>8</v>
@@ -3123,16 +3173,16 @@
     </row>
     <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>119</v>
+        <v>129</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>8</v>
@@ -3140,16 +3190,16 @@
     </row>
     <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>119</v>
+        <v>130</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>8</v>
@@ -3157,16 +3207,16 @@
     </row>
     <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>119</v>
+        <v>131</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>8</v>
@@ -3174,16 +3224,16 @@
     </row>
     <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>119</v>
+        <v>132</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>8</v>
@@ -3191,16 +3241,16 @@
     </row>
     <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>119</v>
+        <v>133</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>8</v>
@@ -3208,16 +3258,16 @@
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>119</v>
+        <v>134</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>8</v>
@@ -3225,16 +3275,16 @@
     </row>
     <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>119</v>
+        <v>135</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>8</v>
@@ -3242,16 +3292,16 @@
     </row>
     <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>119</v>
+        <v>136</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>8</v>
@@ -3259,16 +3309,16 @@
     </row>
     <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>119</v>
+        <v>137</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>8</v>
@@ -3276,16 +3326,16 @@
     </row>
     <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>8</v>
@@ -3293,16 +3343,16 @@
     </row>
     <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>119</v>
+        <v>139</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>8</v>
@@ -3310,16 +3360,16 @@
     </row>
     <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>119</v>
+        <v>140</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>8</v>
@@ -3327,16 +3377,16 @@
     </row>
     <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>119</v>
+        <v>141</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>8</v>
@@ -3344,16 +3394,16 @@
     </row>
     <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>8</v>
@@ -3361,16 +3411,16 @@
     </row>
     <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>119</v>
+        <v>143</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>8</v>
@@ -3378,16 +3428,16 @@
     </row>
     <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>119</v>
+        <v>144</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>8</v>
@@ -3395,16 +3445,16 @@
     </row>
     <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>119</v>
+        <v>145</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>8</v>
@@ -3412,16 +3462,16 @@
     </row>
     <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>8</v>
@@ -3429,16 +3479,16 @@
     </row>
     <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>8</v>
@@ -3446,16 +3496,16 @@
     </row>
     <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>8</v>
@@ -3463,16 +3513,16 @@
     </row>
     <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>8</v>
@@ -3480,16 +3530,16 @@
     </row>
     <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>8</v>
@@ -3497,16 +3547,16 @@
     </row>
     <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>8</v>
@@ -3514,16 +3564,16 @@
     </row>
     <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>8</v>
@@ -3531,84 +3581,84 @@
     </row>
     <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>8</v>
@@ -3616,16 +3666,16 @@
     </row>
     <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>8</v>
@@ -3633,16 +3683,16 @@
     </row>
     <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>8</v>
@@ -3650,16 +3700,16 @@
     </row>
     <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>8</v>
@@ -3667,16 +3717,16 @@
     </row>
     <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>8</v>
@@ -3684,16 +3734,16 @@
     </row>
     <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>8</v>
@@ -3701,16 +3751,16 @@
     </row>
     <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>8</v>
@@ -3718,16 +3768,16 @@
     </row>
     <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>8</v>
@@ -3735,16 +3785,16 @@
     </row>
     <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>8</v>
@@ -3752,16 +3802,16 @@
     </row>
     <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>8</v>
@@ -3769,16 +3819,16 @@
     </row>
     <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>8</v>
@@ -3786,16 +3836,16 @@
     </row>
     <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>8</v>
@@ -3803,16 +3853,16 @@
     </row>
     <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>8</v>
@@ -3820,16 +3870,16 @@
     </row>
     <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>8</v>
@@ -3837,16 +3887,16 @@
     </row>
     <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>8</v>
@@ -3854,16 +3904,16 @@
     </row>
     <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>8</v>
@@ -3871,16 +3921,16 @@
     </row>
     <row r="149" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>8</v>
@@ -3888,16 +3938,16 @@
     </row>
     <row r="150" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>8</v>
@@ -3905,16 +3955,16 @@
     </row>
     <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>8</v>
@@ -3922,16 +3972,16 @@
     </row>
     <row r="152" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>8</v>
@@ -3939,67 +3989,67 @@
     </row>
     <row r="153" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>8</v>
@@ -4007,16 +4057,16 @@
     </row>
     <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>8</v>
@@ -4024,16 +4074,16 @@
     </row>
     <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>8</v>
@@ -4041,16 +4091,16 @@
     </row>
     <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>8</v>
@@ -4058,33 +4108,33 @@
     </row>
     <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>8</v>
@@ -4092,16 +4142,16 @@
     </row>
     <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>8</v>
@@ -4109,33 +4159,33 @@
     </row>
     <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="5" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>8</v>
@@ -4143,33 +4193,33 @@
     </row>
     <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>8</v>
@@ -4177,543 +4227,543 @@
     </row>
     <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="5" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="5" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="5" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="5" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="5" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>8</v>
@@ -4721,16 +4771,16 @@
     </row>
     <row r="199" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>8</v>
@@ -4738,16 +4788,16 @@
     </row>
     <row r="200" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>8</v>
@@ -4755,16 +4805,16 @@
     </row>
     <row r="201" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>8</v>
@@ -4772,526 +4822,526 @@
     </row>
     <row r="202" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
+      </c>
+      <c r="C232" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D232" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>8</v>
@@ -5299,16 +5349,16 @@
     </row>
     <row r="233" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C233" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D233" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>8</v>
@@ -5316,16 +5366,16 @@
     </row>
     <row r="234" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C234" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D234" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>8</v>
@@ -5333,16 +5383,16 @@
     </row>
     <row r="235" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C235" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D235" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>8</v>
@@ -5350,16 +5400,16 @@
     </row>
     <row r="236" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C236" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D236" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>8</v>
@@ -5367,16 +5417,16 @@
     </row>
     <row r="237" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C237" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D237" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>8</v>
@@ -5384,16 +5434,16 @@
     </row>
     <row r="238" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D238" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C238" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D238" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>8</v>
@@ -5401,16 +5451,16 @@
     </row>
     <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C239" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C239" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D239" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>8</v>
@@ -5418,16 +5468,16 @@
     </row>
     <row r="240" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C240" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D240" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C240" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D240" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>8</v>
@@ -5435,16 +5485,16 @@
     </row>
     <row r="241" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C241" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D241" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C241" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D241" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>8</v>
@@ -5452,16 +5502,16 @@
     </row>
     <row r="242" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C242" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D242" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>8</v>
@@ -5469,16 +5519,16 @@
     </row>
     <row r="243" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C243" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D243" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>8</v>
@@ -5486,16 +5536,16 @@
     </row>
     <row r="244" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C244" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D244" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>8</v>
@@ -5503,16 +5553,16 @@
     </row>
     <row r="245" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C245" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D245" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>8</v>
@@ -5520,22 +5570,38 @@
     </row>
     <row r="246" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="C246" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D246" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E246">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Beta lactam and related"/>
+        <filter val="Glycopeptides"/>
+        <filter val="Imidazoles"/>
+        <filter val="MLS"/>
+        <filter val="Nitrofuran derivatives"/>
+        <filter val="Qinolones/fluoroquinolones"/>
+        <filter val="Rifamycins"/>
+        <filter val="Sulfonamides/Trimethoprim derivatives and their combinations"/>
+        <filter val="other"/>
+        <filter val="tetracyclines and related"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5543,5 +5609,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>